--- a/results 3 workers/Results 3 workers.xlsx
+++ b/results 3 workers/Results 3 workers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumentumok_2026\PS\Revision\Logs Results revision\results 3 workers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumentumok_2026\PS\Revision\For resubmit\Repository\results 3 workers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B411254D-DDBB-46ED-B451-9D1178FC101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA962E68-F7C8-4D96-92F2-D6E57C93F0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,8 +750,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - 1. jelölőszín 2" xfId="20" xr:uid="{C853FAF1-633E-473F-81D7-BBE282D96D69}"/>
@@ -1354,7 +1354,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1416,7 +1416,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="[&gt;=10000]#,##0;0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3874,10 +3874,10 @@
       <c r="D39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G39" s="16"/>
+      <c r="G39" s="15"/>
       <c r="S39" s="3">
         <v>15800</v>
       </c>
@@ -3890,11 +3890,11 @@
       <c r="D40" s="3">
         <v>15359.740968215299</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="15">
         <f>MAX(D40:D49)</f>
         <v>15359.740968215299</v>
       </c>
-      <c r="G40" s="16"/>
+      <c r="G40" s="15"/>
       <c r="S40" s="3">
         <v>15600</v>
       </c>
@@ -3919,10 +3919,10 @@
       <c r="D42" s="5">
         <v>15138.9227542836</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="16"/>
+      <c r="G42" s="15"/>
       <c r="S42" s="3">
         <v>15200</v>
       </c>
@@ -3935,11 +3935,11 @@
       <c r="D43" s="5">
         <v>14980.512580292299</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="15">
         <f>MIN(D40:D49)</f>
         <v>14817.7730879675</v>
       </c>
-      <c r="G43" s="16"/>
+      <c r="G43" s="15"/>
       <c r="S43" s="3">
         <v>15000</v>
       </c>
@@ -3964,10 +3964,10 @@
       <c r="D45" s="5">
         <v>15228.996646103</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="F45" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="16"/>
+      <c r="G45" s="15"/>
       <c r="S45" s="3">
         <v>14600</v>
       </c>
@@ -3977,11 +3977,11 @@
       <c r="D46" s="5">
         <v>15315.973072000501</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="15">
         <f>MEDIAN(D40:D49)</f>
         <v>15122.03739805415</v>
       </c>
-      <c r="G46" s="16"/>
+      <c r="G46" s="15"/>
     </row>
     <row r="47" spans="4:23" x14ac:dyDescent="0.25">
       <c r="D47" s="5">
@@ -3992,37 +3992,37 @@
       <c r="D48" s="5">
         <v>15218.1794787119</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F48" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G48" s="16"/>
+      <c r="G48" s="15"/>
       <c r="S48" s="13"/>
       <c r="T48" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="V48" s="16" t="s">
+      <c r="V48" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="W48" s="16"/>
+      <c r="W48" s="15"/>
     </row>
     <row r="49" spans="3:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D49" s="6">
         <v>15063.9511343871</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="15">
         <f>STDEVA(D40:D49)</f>
         <v>160.69344428559225</v>
       </c>
-      <c r="G49" s="16"/>
+      <c r="G49" s="15"/>
       <c r="S49" s="13"/>
       <c r="T49" s="9">
         <v>14492.7296592278</v>
       </c>
-      <c r="V49" s="16">
+      <c r="V49" s="15">
         <f>MAX(T49:T58)</f>
         <v>14662.753707816601</v>
       </c>
-      <c r="W49" s="16"/>
+      <c r="W49" s="15"/>
     </row>
     <row r="50" spans="3:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D50" s="4">
@@ -4039,31 +4039,31 @@
       <c r="T51" s="10">
         <v>14219.7814105542</v>
       </c>
-      <c r="V51" s="16" t="s">
+      <c r="V51" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="W51" s="16"/>
+      <c r="W51" s="15"/>
     </row>
     <row r="52" spans="3:23" x14ac:dyDescent="0.25">
       <c r="S52" s="14"/>
       <c r="T52" s="10">
         <v>14445.692924245001</v>
       </c>
-      <c r="V52" s="16">
+      <c r="V52" s="15">
         <f>MIN(T49:T58)</f>
         <v>14219.7814105542</v>
       </c>
-      <c r="W52" s="16"/>
+      <c r="W52" s="15"/>
     </row>
     <row r="53" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="F53" s="16" t="s">
+      <c r="D53" s="15"/>
+      <c r="F53" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G53" s="16"/>
+      <c r="G53" s="15"/>
       <c r="S53" s="14"/>
       <c r="T53" s="10">
         <v>14237.291567374299</v>
@@ -4086,21 +4086,21 @@
       <c r="T54" s="10">
         <v>14539.583773709101</v>
       </c>
-      <c r="V54" s="16" t="s">
+      <c r="V54" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="W54" s="16"/>
+      <c r="W54" s="15"/>
     </row>
     <row r="55" spans="3:23" x14ac:dyDescent="0.25">
       <c r="S55" s="14"/>
       <c r="T55" s="10">
         <v>14417.767928072901</v>
       </c>
-      <c r="V55" s="16">
+      <c r="V55" s="15">
         <f>MEDIAN(T49:T58)</f>
         <v>14469.211291736399</v>
       </c>
-      <c r="W55" s="16"/>
+      <c r="W55" s="15"/>
     </row>
     <row r="56" spans="3:23" x14ac:dyDescent="0.25">
       <c r="S56" s="14"/>
@@ -4116,10 +4116,10 @@
       <c r="T57" s="10">
         <v>14384.80684155</v>
       </c>
-      <c r="V57" s="16" t="s">
+      <c r="V57" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="W57" s="16"/>
+      <c r="W57" s="15"/>
     </row>
     <row r="58" spans="3:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D58" s="5">
@@ -4129,11 +4129,11 @@
       <c r="T58" s="11">
         <v>14578.5867114669</v>
       </c>
-      <c r="V58" s="16">
+      <c r="V58" s="15">
         <f>STDEVA(T49:T58)</f>
         <v>152.91524658765638</v>
       </c>
-      <c r="W58" s="16"/>
+      <c r="W58" s="15"/>
     </row>
     <row r="59" spans="3:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D59" s="5">
@@ -4154,19 +4154,19 @@
       <c r="D61" s="5">
         <v>6395.5472</v>
       </c>
-      <c r="S61" s="15"/>
-      <c r="T61" s="15"/>
+      <c r="S61" s="16"/>
+      <c r="T61" s="16"/>
     </row>
     <row r="62" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D62" s="5">
         <v>6611.6350000000002</v>
       </c>
-      <c r="S62" s="16" t="s">
+      <c r="S62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="T62" s="16"/>
-      <c r="U62" s="15"/>
-      <c r="V62" s="15"/>
+      <c r="T62" s="15"/>
+      <c r="U62" s="16"/>
+      <c r="V62" s="16"/>
     </row>
     <row r="63" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D63" s="5">
@@ -4409,16 +4409,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
     <mergeCell ref="U62:V62"/>
     <mergeCell ref="S62:T62"/>
     <mergeCell ref="S61:T61"/>
@@ -4430,6 +4420,16 @@
     <mergeCell ref="V55:W55"/>
     <mergeCell ref="V57:W57"/>
     <mergeCell ref="V58:W58"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
